--- a/knowledge_source/finance/excel/finance.xlsx
+++ b/knowledge_source/finance/excel/finance.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nielsenenterprise-my.sharepoint.com/personal/bavenraj_partipan_nielseniq_com/Documents/Hackfest Dataset/RAG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paba4001\Downloads\quintelligence\knowledge_source\finance\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1165" documentId="11_F25DC773A252ABDACC10488DE1D858BA5BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62624123-63B4-416D-9B82-26AB0875004E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE99513E-58C2-49F6-9DB4-E2DCCD4A12A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="770" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3944,7 +3944,7 @@
         <v>310</v>
       </c>
       <c r="C1" t="s">
-        <v>412</v>
+        <v>163</v>
       </c>
       <c r="D1" t="s">
         <v>158</v>
